--- a/campus-placement/qa/C-5-Tabular-Screens-CSV-Upload-Validation.xlsx
+++ b/campus-placement/qa/C-5-Tabular-Screens-CSV-Upload-Validation.xlsx
@@ -653,15 +653,11 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -732,15 +728,11 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -811,15 +803,11 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -890,15 +878,11 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
